--- a/data/trans_orig/ED_ADU-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/ED_ADU-Habitat-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Edad media del adulto entrevistado</t>
+          <t>Edad media del adulto entrevistado (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>42,46; 45,4</t>
+          <t>42,56; 45,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>45,07; 47,95</t>
+          <t>45,0; 47,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45,61; 48,4</t>
+          <t>45,58; 48,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47,69; 51,61</t>
+          <t>47,9; 51,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>44,72; 47,55</t>
+          <t>44,75; 47,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,6; 49,52</t>
+          <t>46,52; 49,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,23; 51,23</t>
+          <t>48,16; 51,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>49,35; 52,78</t>
+          <t>49,2; 52,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>44,08; 45,99</t>
+          <t>44,14; 46,11</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46,29; 48,23</t>
+          <t>46,29; 48,24</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47,42; 49,38</t>
+          <t>47,26; 49,43</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>49,17; 51,86</t>
+          <t>49,31; 51,75</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>42,39; 44,7</t>
+          <t>42,38; 44,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>42,99; 45,18</t>
+          <t>42,87; 45,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44,48; 46,58</t>
+          <t>44,37; 46,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45,91; 49,32</t>
+          <t>45,83; 49,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>44,55; 46,93</t>
+          <t>44,5; 46,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,5; 46,71</t>
+          <t>44,64; 46,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,77; 49,18</t>
+          <t>46,79; 49,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>48,54; 50,81</t>
+          <t>48,43; 50,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>43,75; 45,35</t>
+          <t>43,76; 45,43</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44,05; 45,74</t>
+          <t>44,02; 45,66</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45,86; 47,6</t>
+          <t>45,87; 47,6</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>47,56; 49,44</t>
+          <t>47,56; 49,41</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>43,19; 45,74</t>
+          <t>43,06; 45,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>42,24; 44,92</t>
+          <t>42,23; 44,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>43,17; 45,78</t>
+          <t>43,28; 45,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>46,63; 50,29</t>
+          <t>46,7; 50,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>45,1; 47,74</t>
+          <t>45,01; 47,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45,35; 47,91</t>
+          <t>45,36; 47,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>44,99; 47,64</t>
+          <t>44,98; 47,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>48,75; 59,45</t>
+          <t>48,72; 60,3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>44,53; 46,36</t>
+          <t>44,4; 46,33</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44,16; 46,01</t>
+          <t>44,15; 46,06</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>44,66; 46,44</t>
+          <t>44,53; 46,35</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>48,59; 56,43</t>
+          <t>48,46; 56,43</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>41,07; 43,31</t>
+          <t>41,14; 43,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>44,01; 46,55</t>
+          <t>44,01; 46,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45,83; 48,08</t>
+          <t>45,84; 48,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47,51; 50,65</t>
+          <t>47,68; 50,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>44,14; 46,44</t>
+          <t>44,11; 46,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,0; 49,37</t>
+          <t>47,02; 49,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,0; 50,46</t>
+          <t>47,99; 50,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>46,96; 51,94</t>
+          <t>46,97; 52,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>43,03; 44,62</t>
+          <t>43,02; 44,61</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>45,98; 47,66</t>
+          <t>45,92; 47,61</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>47,38; 49,03</t>
+          <t>47,21; 48,91</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>47,79; 50,89</t>
+          <t>47,87; 50,84</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>42,78; 44,02</t>
+          <t>42,79; 44,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>44,12; 45,39</t>
+          <t>44,16; 45,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45,43; 46,6</t>
+          <t>45,43; 46,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47,74; 49,38</t>
+          <t>47,7; 49,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>45,13; 46,39</t>
+          <t>45,11; 46,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,41; 47,64</t>
+          <t>46,43; 47,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,57; 48,89</t>
+          <t>47,66; 48,92</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>49,73; 53,93</t>
+          <t>49,79; 53,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>44,15; 45,09</t>
+          <t>44,17; 45,06</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45,5; 46,38</t>
+          <t>45,48; 46,36</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46,71; 47,6</t>
+          <t>46,73; 47,57</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>49,09; 51,75</t>
+          <t>49,09; 51,61</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/ED_ADU-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/ED_ADU-Habitat-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49,87</t>
+          <t>50,42</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>51,28</t>
+          <t>51,7</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>50,62</t>
+          <t>51,08</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>42,56; 45,39</t>
+          <t>42,57; 45,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>45,0; 47,74</t>
+          <t>45,05; 47,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45,58; 48,44</t>
+          <t>45,66; 48,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47,9; 51,84</t>
+          <t>48,56; 52,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>44,75; 47,73</t>
+          <t>44,71; 47,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,52; 49,43</t>
+          <t>46,52; 49,51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,16; 51,24</t>
+          <t>48,33; 51,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>49,2; 52,66</t>
+          <t>50,3; 52,91</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>44,14; 46,11</t>
+          <t>44,06; 46,05</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46,29; 48,24</t>
+          <t>46,31; 48,33</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47,26; 49,43</t>
+          <t>47,49; 49,36</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>49,31; 51,75</t>
+          <t>50,11; 52,13</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>47,51</t>
+          <t>46,68</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>49,71</t>
+          <t>49,48</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>48,49</t>
+          <t>48,09</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>42,38; 44,61</t>
+          <t>42,45; 44,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>42,87; 45,19</t>
+          <t>42,98; 45,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44,37; 46,67</t>
+          <t>44,45; 46,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45,83; 49,33</t>
+          <t>45,35; 47,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>44,5; 46,92</t>
+          <t>44,48; 46,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,64; 46,96</t>
+          <t>44,42; 46,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,79; 49,2</t>
+          <t>46,76; 49,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>48,43; 50,79</t>
+          <t>48,34; 50,61</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>43,76; 45,43</t>
+          <t>43,71; 45,43</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44,02; 45,66</t>
+          <t>43,98; 45,63</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45,87; 47,6</t>
+          <t>45,92; 47,58</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>47,56; 49,41</t>
+          <t>47,26; 48,97</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>48,59</t>
+          <t>48,76</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>53,06</t>
+          <t>48,77</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>51,14</t>
+          <t>48,76</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>43,06; 45,7</t>
+          <t>43,15; 45,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>42,23; 44,85</t>
+          <t>42,24; 45,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>43,28; 45,99</t>
+          <t>43,34; 45,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>46,7; 50,29</t>
+          <t>47,07; 50,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>45,01; 47,77</t>
+          <t>44,96; 47,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45,36; 47,93</t>
+          <t>45,27; 47,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>44,98; 47,61</t>
+          <t>44,87; 47,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>48,72; 60,3</t>
+          <t>47,33; 50,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>44,4; 46,33</t>
+          <t>44,38; 46,3</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44,15; 46,06</t>
+          <t>44,19; 45,99</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>44,53; 46,35</t>
+          <t>44,48; 46,33</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>48,46; 56,43</t>
+          <t>47,74; 49,71</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49,12</t>
+          <t>48,93</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>50,31</t>
+          <t>51,08</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>49,77</t>
+          <t>50,07</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>41,14; 43,4</t>
+          <t>41,17; 43,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>44,01; 46,41</t>
+          <t>44,1; 46,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45,84; 48,1</t>
+          <t>45,77; 47,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47,68; 50,54</t>
+          <t>47,47; 50,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>44,11; 46,4</t>
+          <t>44,13; 46,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,02; 49,35</t>
+          <t>46,96; 49,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,99; 50,29</t>
+          <t>47,96; 50,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>46,97; 52,01</t>
+          <t>49,87; 52,29</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>43,02; 44,61</t>
+          <t>43,01; 44,61</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>45,92; 47,61</t>
+          <t>45,86; 47,57</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>47,21; 48,91</t>
+          <t>47,32; 48,9</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>47,87; 50,84</t>
+          <t>49,15; 50,94</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>48,59</t>
+          <t>48,51</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>51,04</t>
+          <t>50,24</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>49,86</t>
+          <t>49,4</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>42,79; 44,04</t>
+          <t>42,8; 44,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>44,16; 45,35</t>
+          <t>44,1; 45,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45,43; 46,58</t>
+          <t>45,4; 46,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47,7; 49,36</t>
+          <t>47,8; 49,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>45,11; 46,39</t>
+          <t>45,18; 46,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,43; 47,66</t>
+          <t>46,43; 47,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,66; 48,92</t>
+          <t>47,6; 48,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>49,79; 53,85</t>
+          <t>49,65; 50,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>44,17; 45,06</t>
+          <t>44,13; 45,06</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45,48; 46,36</t>
+          <t>45,56; 46,41</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46,73; 47,57</t>
+          <t>46,76; 47,64</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>49,09; 51,61</t>
+          <t>48,96; 49,88</t>
         </is>
       </c>
     </row>
